--- a/out/27S/ver1/27S_ver1_room.xlsx
+++ b/out/27S/ver1/27S_ver1_room.xlsx
@@ -11,15 +11,18 @@
     <sheet name="Corley 102" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Corley 103" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Corley 104" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Corley 268" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Ross Pendergraft Library 220" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Ross Pendergraft Library 331" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Rothwell 206" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Rothwell 207" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Rothwell 212" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Rothwell 213" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Rothwell 221" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Rothwell 306" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Corley 267" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Corley 268" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Corley 269" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Ross Pendergraft Library 220" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Ross Pendergraft Library 331" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Rothwell 206" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Rothwell 207" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Rothwell 212" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Rothwell 213" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Rothwell 221" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Rothwell 306" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Rothwell 312" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Corley 101'!$A$2:$F$20</definedName>
@@ -30,24 +33,30 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Corley 103'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Corley 104'!$A$2:$F$20</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Corley 104'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Corley 268'!$A$2:$F$20</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Corley 268'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Ross Pendergraft Library 220'!$A$2:$F$20</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Ross Pendergraft Library 220'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Ross Pendergraft Library 331'!$A$2:$F$20</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Ross Pendergraft Library 331'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Rothwell 206'!$A$2:$F$20</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Rothwell 206'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Rothwell 207'!$A$2:$F$20</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Rothwell 207'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Rothwell 212'!$A$2:$F$20</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Rothwell 212'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Rothwell 213'!$A$2:$F$20</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Rothwell 213'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Rothwell 221'!$A$2:$F$20</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="11">'Rothwell 221'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Rothwell 306'!$A$2:$F$20</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="12">'Rothwell 306'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Corley 267'!$A$2:$F$20</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Corley 267'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Corley 268'!$A$2:$F$20</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Corley 268'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Corley 269'!$A$2:$F$20</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Corley 269'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Ross Pendergraft Library 220'!$A$2:$F$20</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Ross Pendergraft Library 220'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ross Pendergraft Library 331'!$A$2:$F$20</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Ross Pendergraft Library 331'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Rothwell 206'!$A$2:$F$20</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Rothwell 206'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Rothwell 207'!$A$2:$F$20</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Rothwell 207'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Rothwell 212'!$A$2:$F$20</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="11">'Rothwell 212'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Rothwell 213'!$A$2:$F$20</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="12">'Rothwell 213'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Rothwell 221'!$A$2:$F$20</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="13">'Rothwell 221'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Rothwell 306'!$A$2:$F$20</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="14">'Rothwell 306'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Rothwell 312'!$A$2:$F$20</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="15">'Rothwell 312'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -78,7 +87,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -97,7 +106,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE6F2"/>
+        <fgColor rgb="00E6F3FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -107,7 +116,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E6F3FF"/>
+        <fgColor rgb="00FFE6F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -117,17 +126,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF2E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFFACD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2E6"/>
+        <fgColor rgb="00F0E6FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F0E6FF"/>
+        <fgColor rgb="00F5F5DC"/>
       </patternFill>
     </fill>
   </fills>
@@ -185,7 +199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -208,16 +222,19 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -643,24 +660,24 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>MATH 2934-002
-Xiao, Xinli
+          <t>MATH 1914-001
+Cox, Allie M.
 8:00 AM-8:50 AM</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>MATH 2934-002
-Xiao, Xinli
+          <t>MATH 1914-001
+Cox, Allie M.
 8:00 AM-8:50 AM</t>
         </is>
       </c>
       <c r="E3" s="5" t="n"/>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>MATH 2934-002
-Xiao, Xinli
+          <t>MATH 1914-001
+Cox, Allie M.
 8:00 AM-8:50 AM</t>
         </is>
       </c>
@@ -714,13 +731,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n"/>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>MATH 1914-001
-Cox, Allie M.
-9:30 AM-10:50 AM</t>
-        </is>
-      </c>
+      <c r="C6" s="5" t="n"/>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="7" t="inlineStr">
         <is>
@@ -739,24 +750,24 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>MATH 1914-001
-Cox, Allie M.
+          <t>MATH 2703-001
+Jordan, Susan M.
 10:00 AM-10:50 AM</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n"/>
+      <c r="C7" s="5" t="n"/>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>MATH 1914-001
-Cox, Allie M.
+          <t>MATH 2703-001
+Jordan, Susan M.
 10:00 AM-10:50 AM</t>
         </is>
       </c>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>MATH 1914-001
-Cox, Allie M.
+          <t>MATH 2703-001
+Jordan, Susan M.
 10:00 AM-10:50 AM</t>
         </is>
       </c>
@@ -768,7 +779,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
+      <c r="C8" s="5" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
@@ -781,36 +792,36 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>MATH 2703-001
-Limperis, Thomas G.
+          <t>MATH 2914-002
+Jordan, Susan M.
 11:00 AM-11:50 AM</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>MATH 4971-001
-Xiao, Xinli
+          <t>MATH 2703-002
+Jordan, Susan M.
 11:00 AM-12:20 PM</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>MATH 2703-001
-Limperis, Thomas G.
+          <t>MATH 2914-002
+Jordan, Susan M.
 11:00 AM-11:50 AM</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>MATH 2934-002
-Xiao, Xinli
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>MATH 2703-002
+Jordan, Susan M.
 11:00 AM-12:20 PM</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>MATH 2703-001
-Limperis, Thomas G.
+          <t>MATH 2914-002
+Jordan, Susan M.
 11:00 AM-11:50 AM</t>
         </is>
       </c>
@@ -859,7 +870,7 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>MATH 2914-002
+          <t>MATH 1003-007
 Jordan, Susan M.
 1:00 PM-1:50 PM</t>
         </is>
@@ -867,12 +878,12 @@
       <c r="C13" s="5" t="n"/>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>MATH 2914-002
+          <t>MATH 1003-007
 Jordan, Susan M.
 1:00 PM-1:50 PM</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>MATH 2914-002
 Jordan, Susan M.
@@ -881,7 +892,7 @@
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>MATH 2914-002
+          <t>MATH 1003-007
 Jordan, Susan M.
 1:00 PM-1:50 PM</t>
         </is>
@@ -997,7 +1008,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:F20"/>
-  <mergeCells count="25">
+  <mergeCells count="24">
     <mergeCell ref="F15:F16"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="F3:F4"/>
@@ -1007,7 +1018,6 @@
     <mergeCell ref="D13:D14"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="D3:D4"/>
-    <mergeCell ref="C6:C8"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="F13:F14"/>
     <mergeCell ref="B9:B10"/>
@@ -1016,8 +1026,8 @@
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="E6:E8"/>
+    <mergeCell ref="D5:D6"/>
     <mergeCell ref="E13:E15"/>
-    <mergeCell ref="D5:D6"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="F7:F8"/>
@@ -1049,7 +1059,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Room Schedule -- Rothwell 212</t>
+          <t>Room Schedule -- Rothwell 206</t>
         </is>
       </c>
     </row>
@@ -1091,11 +1101,29 @@
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n"/>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>MATH 2924-002
+Xiao, Xinli
+8:00 AM-8:50 AM</t>
+        </is>
+      </c>
       <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>MATH 2924-002
+Xiao, Xinli
+8:00 AM-8:50 AM</t>
+        </is>
+      </c>
       <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>MATH 2924-002
+Xiao, Xinli
+8:00 AM-8:50 AM</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -1103,11 +1131,11 @@
           <t>8:30 AM</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
+      <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
+      <c r="D4" s="6" t="n"/>
       <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
+      <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -1115,26 +1143,26 @@
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>MATH 3243-002
-Overduin, Matthew D.
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>MATH 4003-001
+Xiao, Xinli
 9:00 AM-9:50 AM</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>MATH 3243-002
-Overduin, Matthew D.
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>MATH 4003-001
+Xiao, Xinli
 9:00 AM-9:50 AM</t>
         </is>
       </c>
       <c r="E5" s="5" t="n"/>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>MATH 3243-002
-Overduin, Matthew D.
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>MATH 4003-001
+Xiao, Xinli
 9:00 AM-9:50 AM</t>
         </is>
       </c>
@@ -1148,7 +1176,13 @@
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="5" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="5" t="n"/>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>MATH 2924-003
+Limperis, Thomas G.
+9:30 AM-10:50 AM</t>
+        </is>
+      </c>
       <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -1157,11 +1191,29 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n"/>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>MATH 3243-001
+Xiao, Xinli
+10:00 AM-10:50 AM</t>
+        </is>
+      </c>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>MATH 3243-001
+Xiao, Xinli
+10:00 AM-10:50 AM</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>MATH 3243-001
+Xiao, Xinli
+10:00 AM-10:50 AM</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -1169,11 +1221,11 @@
           <t>10:30 AM</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n"/>
+      <c r="B8" s="6" t="n"/>
       <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -1230,7 +1282,13 @@
         </is>
       </c>
       <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>MATH 2924-002
+Xiao, Xinli
+1:00 PM-2:20 PM</t>
+        </is>
+      </c>
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
@@ -1242,7 +1300,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
+      <c r="C14" s="9" t="n"/>
       <c r="D14" s="5" t="n"/>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
@@ -1254,7 +1312,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
+      <c r="C15" s="6" t="n"/>
       <c r="D15" s="5" t="n"/>
       <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n"/>
@@ -1321,10 +1379,18 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:F20"/>
-  <mergeCells count="4">
+  <mergeCells count="12">
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
+    <mergeCell ref="E6:E8"/>
     <mergeCell ref="B5:B6"/>
-    <mergeCell ref="A1:F1"/>
     <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1352,7 +1418,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Room Schedule -- Rothwell 213</t>
+          <t>Room Schedule -- Rothwell 207</t>
         </is>
       </c>
     </row>
@@ -1418,11 +1484,29 @@
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n"/>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>STAT 3153-001
+Jordan, Scott M.
+9:00 AM-9:50 AM</t>
+        </is>
+      </c>
       <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>STAT 3153-001
+Jordan, Scott M.
+9:00 AM-9:50 AM</t>
+        </is>
+      </c>
       <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>STAT 3153-001
+Jordan, Scott M.
+9:00 AM-9:50 AM</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -1430,11 +1514,17 @@
           <t>9:30 AM</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>MATH 2934-001
+Staff 2
+9:30 AM-10:50 AM</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n"/>
       <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
+      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -1442,11 +1532,29 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>MATH 2934-001
+Staff 2
+10:00 AM-10:50 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>MATH 2934-001
+Staff 2
+10:00 AM-10:50 AM</t>
+        </is>
+      </c>
       <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>MATH 2934-001
+Staff 2
+10:00 AM-10:50 AM</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -1454,11 +1562,11 @@
           <t>10:30 AM</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
       <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="F8" s="6" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -1466,29 +1574,11 @@
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>STAT 3113-001
-Xiao, Xinli
-11:00 AM-11:50 AM</t>
-        </is>
-      </c>
+      <c r="B9" s="5" t="n"/>
       <c r="C9" s="5" t="n"/>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>STAT 3113-001
-Xiao, Xinli
-11:00 AM-11:50 AM</t>
-        </is>
-      </c>
+      <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n"/>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>STAT 3113-001
-Xiao, Xinli
-11:00 AM-11:50 AM</t>
-        </is>
-      </c>
+      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -1496,11 +1586,11 @@
           <t>11:30 AM</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
+      <c r="B10" s="5" t="n"/>
       <c r="C10" s="5" t="n"/>
-      <c r="D10" s="6" t="n"/>
+      <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
-      <c r="F10" s="6" t="n"/>
+      <c r="F10" s="5" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -1532,29 +1622,11 @@
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>STAT 3183-001
-Jordan, Scott M.
-1:00 PM-1:50 PM</t>
-        </is>
-      </c>
+      <c r="B13" s="5" t="n"/>
       <c r="C13" s="5" t="n"/>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>STAT 3183-001
-Jordan, Scott M.
-1:00 PM-1:50 PM</t>
-        </is>
-      </c>
+      <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>STAT 3183-001
-Jordan, Scott M.
-1:00 PM-1:50 PM</t>
-        </is>
-      </c>
+      <c r="F13" s="5" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -1562,11 +1634,11 @@
           <t>1:30 PM</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n"/>
+      <c r="B14" s="5" t="n"/>
       <c r="C14" s="5" t="n"/>
-      <c r="D14" s="6" t="n"/>
+      <c r="D14" s="5" t="n"/>
       <c r="E14" s="5" t="n"/>
-      <c r="F14" s="6" t="n"/>
+      <c r="F14" s="5" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -1642,14 +1714,15 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:F20"/>
-  <mergeCells count="7">
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="B13:B14"/>
+  <mergeCells count="8">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -1676,7 +1749,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Room Schedule -- Rothwell 221</t>
+          <t>Room Schedule -- Rothwell 212</t>
         </is>
       </c>
     </row>
@@ -1742,26 +1815,26 @@
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>MATH 1003-006
-King, Jamie L.
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>MATH 3243-002
+Limperis, Thomas G.
 9:00 AM-9:50 AM</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>MATH 1003-006
-King, Jamie L.
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>MATH 3243-002
+Limperis, Thomas G.
 9:00 AM-9:50 AM</t>
         </is>
       </c>
       <c r="E5" s="5" t="n"/>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>MATH 1003-006
-King, Jamie L.
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>MATH 3243-002
+Limperis, Thomas G.
 9:00 AM-9:50 AM</t>
         </is>
       </c>
@@ -1784,29 +1857,11 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>STAT 2163-001
-King, Jamie L.
-10:00 AM-10:50 AM</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="n"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>STAT 2163-001
-King, Jamie L.
-10:00 AM-10:50 AM</t>
-        </is>
-      </c>
+      <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>STAT 2163-001
-King, Jamie L.
-10:00 AM-10:50 AM</t>
-        </is>
-      </c>
+      <c r="F7" s="5" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -1814,11 +1869,11 @@
           <t>10:30 AM</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
+      <c r="B8" s="5" t="n"/>
       <c r="C8" s="5" t="n"/>
-      <c r="D8" s="6" t="n"/>
+      <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
-      <c r="F8" s="6" t="n"/>
+      <c r="F8" s="5" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -1874,29 +1929,11 @@
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>MATH 1113-003
-Cox, Allie M.
-1:00 PM-1:50 PM</t>
-        </is>
-      </c>
+      <c r="B13" s="5" t="n"/>
       <c r="C13" s="5" t="n"/>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>MATH 1113-003
-Cox, Allie M.
-1:00 PM-1:50 PM</t>
-        </is>
-      </c>
+      <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>MATH 1113-003
-Cox, Allie M.
-1:00 PM-1:50 PM</t>
-        </is>
-      </c>
+      <c r="F13" s="5" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -1904,11 +1941,11 @@
           <t>1:30 PM</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n"/>
+      <c r="B14" s="5" t="n"/>
       <c r="C14" s="5" t="n"/>
-      <c r="D14" s="6" t="n"/>
+      <c r="D14" s="5" t="n"/>
       <c r="E14" s="5" t="n"/>
-      <c r="F14" s="6" t="n"/>
+      <c r="F14" s="5" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -1916,21 +1953,9 @@
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>MATH 1110-003
-Cox, Allie M.
-2:00 PM-2:50 PM</t>
-        </is>
-      </c>
+      <c r="B15" s="5" t="n"/>
       <c r="C15" s="5" t="n"/>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>MATH 1110-003
-Cox, Allie M.
-2:00 PM-2:50 PM</t>
-        </is>
-      </c>
+      <c r="D15" s="5" t="n"/>
       <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n"/>
     </row>
@@ -1940,9 +1965,9 @@
           <t>2:30 PM</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n"/>
+      <c r="B16" s="5" t="n"/>
       <c r="C16" s="5" t="n"/>
-      <c r="D16" s="6" t="n"/>
+      <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
     </row>
@@ -1996,18 +2021,10 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:F20"/>
-  <mergeCells count="12">
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="F7:F8"/>
+  <mergeCells count="4">
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="B5:B6"/>
-    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2035,7 +2052,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Room Schedule -- Rothwell 306</t>
+          <t>Room Schedule -- Rothwell 213</t>
         </is>
       </c>
     </row>
@@ -2125,7 +2142,697 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>10:30 AM</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>11:00 AM</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>STAT 3113-001
+Xiao, Xinli
+11:00 AM-11:50 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>STAT 3113-001
+Xiao, Xinli
+11:00 AM-11:50 AM</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>STAT 3113-001
+Xiao, Xinli
+11:00 AM-11:50 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>11:30 AM</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="6" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>12:30 PM</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>STAT 3183-001
+Jordan, Scott M.
+1:00 PM-1:50 PM</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>STAT 3183-001
+Jordan, Scott M.
+1:00 PM-1:50 PM</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>STAT 3183-001
+Jordan, Scott M.
+1:00 PM-1:50 PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>1:30 PM</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="6" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>2:30 PM</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>3:30 PM</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>4:30 PM</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:F20"/>
+  <mergeCells count="7">
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D13:D14"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Schedule -- Rothwell 221</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>8:00 AM</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>8:30 AM</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>MATH 1003-006
+King, Jamie L.
+9:00 AM-9:50 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>MATH 1003-006
+King, Jamie L.
+9:00 AM-9:50 AM</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>MATH 1003-006
+King, Jamie L.
+9:00 AM-9:50 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>9:30 AM</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="6" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>STAT 2163-001
+King, Jamie L.
+10:00 AM-10:50 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>STAT 2163-001
+King, Jamie L.
+10:00 AM-10:50 AM</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>STAT 2163-001
+King, Jamie L.
+10:00 AM-10:50 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>10:30 AM</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>11:00 AM</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>MATH 4971-001
+Xiao, Xinli
+11:00 AM-12:20 PM</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>11:30 AM</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>12:30 PM</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>MATH 1113-003
+Growns, Landon C.
+1:00 PM-1:50 PM</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>MATH 1113-003
+Growns, Landon C.
+1:00 PM-1:50 PM</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>MATH 1113-003
+Growns, Landon C.
+1:00 PM-1:50 PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>1:30 PM</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="6" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>MATH 1110-003
+Growns, Landon C.
+2:00 PM-2:50 PM</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>MATH 1110-003
+Growns, Landon C.
+2:00 PM-2:50 PM</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>2:30 PM</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>3:30 PM</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>4:30 PM</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:F20"/>
+  <mergeCells count="13">
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="D5:D6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Schedule -- Rothwell 306</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>8:00 AM</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>8:30 AM</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>9:30 AM</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>MATH 2924-003
 Limperis, Thomas G.
@@ -2133,7 +2840,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>MATH 2924-003
 Limperis, Thomas G.
@@ -2141,10 +2848,313 @@
         </is>
       </c>
       <c r="E7" s="5" t="n"/>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>MATH 2924-003
 Limperis, Thomas G.
+10:00 AM-10:50 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>10:30 AM</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>11:00 AM</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>11:30 AM</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>12:30 PM</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>1:30 PM</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>2:30 PM</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>3:30 PM</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>4:30 PM</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:F20"/>
+  <mergeCells count="4">
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="F7:F8"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Schedule -- Rothwell 312</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>8:00 AM</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>8:30 AM</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>9:30 AM</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>MATH 1003-005
+Winn, Janet L.
+10:00 AM-10:50 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>MATH 1003-005
+Winn, Janet L.
+10:00 AM-10:50 AM</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>MATH 1003-005
+Winn, Janet L.
 10:00 AM-10:50 AM</t>
         </is>
       </c>
@@ -2380,11 +3390,29 @@
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n"/>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>MATH 2033-001
+Taylor, Teresa L.
+8:00 AM-8:50 AM</t>
+        </is>
+      </c>
       <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>MATH 2033-001
+Taylor, Teresa L.
+8:00 AM-8:50 AM</t>
+        </is>
+      </c>
       <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>MATH 2033-001
+Taylor, Teresa L.
+8:00 AM-8:50 AM</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -2392,11 +3420,11 @@
           <t>8:30 AM</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
+      <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
+      <c r="D4" s="6" t="n"/>
       <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
+      <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -2404,7 +3432,7 @@
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>MATH 2043-001
 Taylor, Teresa L.
@@ -2412,7 +3440,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>MATH 2043-001
 Taylor, Teresa L.
@@ -2420,7 +3448,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n"/>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>MATH 2043-001
 Taylor, Teresa L.
@@ -2437,7 +3465,7 @@
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="5" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>MATH 1914-003
 Ballard, Kasey L.
@@ -2452,29 +3480,11 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>MATH 2033-001
-Taylor, Teresa L.
-10:00 AM-10:50 AM</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="n"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>MATH 2033-001
-Taylor, Teresa L.
-10:00 AM-10:50 AM</t>
-        </is>
-      </c>
+      <c r="D7" s="5" t="n"/>
       <c r="E7" s="9" t="n"/>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>MATH 2033-001
-Taylor, Teresa L.
-10:00 AM-10:50 AM</t>
-        </is>
-      </c>
+      <c r="F7" s="5" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -2482,11 +3492,11 @@
           <t>10:30 AM</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
+      <c r="B8" s="5" t="n"/>
       <c r="C8" s="5" t="n"/>
-      <c r="D8" s="6" t="n"/>
+      <c r="D8" s="5" t="n"/>
       <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
+      <c r="F8" s="5" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -2494,38 +3504,38 @@
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>STAT 3153-002
-Jordan, Scott M.
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>MATH 2934-002
+Limperis, Thomas G.
 11:00 AM-11:50 AM</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>MATH 3033-001
 Taylor, Teresa L.
 11:00 AM-12:20 PM</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>STAT 3153-002
-Jordan, Scott M.
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>MATH 2934-002
+Limperis, Thomas G.
 11:00 AM-11:50 AM</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>MATH 3033-001
 Taylor, Teresa L.
 11:00 AM-12:20 PM</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
-        <is>
-          <t>STAT 3153-002
-Jordan, Scott M.
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>MATH 2934-002
+Limperis, Thomas G.
 11:00 AM-11:50 AM</t>
         </is>
       </c>
@@ -2620,7 +3630,7 @@
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>MATH 3123-001
 Overduin, Matthew D.
@@ -2628,7 +3638,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n"/>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>MATH 3123-001
 Overduin, Matthew D.
@@ -2636,7 +3646,7 @@
         </is>
       </c>
       <c r="E15" s="6" t="n"/>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F15" s="14" t="inlineStr">
         <is>
           <t>MATH 3123-001
 Overduin, Matthew D.
@@ -2651,9 +3661,21 @@
         </is>
       </c>
       <c r="B16" s="6" t="n"/>
-      <c r="C16" s="5" t="n"/>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>MATH 1113-006
+Taylor, Teresa L.
+2:30 PM-3:50 PM</t>
+        </is>
+      </c>
       <c r="D16" s="6" t="n"/>
-      <c r="E16" s="5" t="n"/>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>MATH 1113-006
+Taylor, Teresa L.
+2:30 PM-3:50 PM</t>
+        </is>
+      </c>
       <c r="F16" s="6" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2663,9 +3685,9 @@
         </is>
       </c>
       <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
+      <c r="C17" s="9" t="n"/>
       <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
+      <c r="E17" s="9" t="n"/>
       <c r="F17" s="5" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2675,9 +3697,9 @@
         </is>
       </c>
       <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
+      <c r="C18" s="6" t="n"/>
       <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
+      <c r="E18" s="6" t="n"/>
       <c r="F18" s="5" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2706,12 +3728,15 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:F20"/>
-  <mergeCells count="20">
+  <mergeCells count="22">
     <mergeCell ref="F15:F16"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="F3:F4"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="B13:B14"/>
+    <mergeCell ref="E16:E18"/>
     <mergeCell ref="D13:D14"/>
-    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="D3:D4"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="F13:F14"/>
     <mergeCell ref="B9:B10"/>
@@ -2719,12 +3744,11 @@
     <mergeCell ref="D9:D10"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="B5:B6"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="E13:E15"/>
     <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="E6:E8"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="C16:C18"/>
     <mergeCell ref="C9:C11"/>
     <mergeCell ref="E9:E11"/>
   </mergeCells>
@@ -2819,7 +3843,7 @@
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>MATH 1003-001
 Winn, Janet L.
@@ -2827,7 +3851,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>MATH 1003-001
 Winn, Janet L.
@@ -2835,7 +3859,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n"/>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>MATH 1003-001
 Winn, Janet L.
@@ -2850,7 +3874,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n"/>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>MATH 0803-001
 Winn, Janet L.
@@ -2858,7 +3882,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>MATH 0803-001
 Winn, Janet L.
@@ -2873,26 +3897,26 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>MATH 2223-003
-Growns, Landon C.
+Cox, Allie M.
 10:00 AM-10:50 AM</t>
         </is>
       </c>
       <c r="C7" s="9" t="n"/>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>MATH 2223-003
-Growns, Landon C.
+Cox, Allie M.
 10:00 AM-10:50 AM</t>
         </is>
       </c>
       <c r="E7" s="9" t="n"/>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>MATH 2223-003
-Growns, Landon C.
+Cox, Allie M.
 10:00 AM-10:50 AM</t>
         </is>
       </c>
@@ -2915,10 +3939,10 @@
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>MATH 2223-001
-Growns, Landon C.
+Cox, Allie M.
 11:00 AM-11:50 AM</t>
         </is>
       </c>
@@ -2929,10 +3953,10 @@
 11:00 AM-12:20 PM</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>MATH 2223-001
-Growns, Landon C.
+Cox, Allie M.
 11:00 AM-11:50 AM</t>
         </is>
       </c>
@@ -2943,10 +3967,10 @@
 11:00 AM-12:20 PM</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>MATH 2223-001
-Growns, Landon C.
+Cox, Allie M.
 11:00 AM-11:50 AM</t>
         </is>
       </c>
@@ -3210,38 +4234,38 @@
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>MATH 0903-002
-Winn, Janet L.
+Growns, Landon C.
 8:00 AM-8:50 AM</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>MATH 1113-002
-Winn, Janet L.
+Growns, Landon C.
 8:00 AM-9:20 AM</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>MATH 0903-002
-Winn, Janet L.
+Growns, Landon C.
 8:00 AM-8:50 AM</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>MATH 1113-002
-Winn, Janet L.
+Growns, Landon C.
 8:00 AM-9:20 AM</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>MATH 0903-002
-Winn, Janet L.
+Growns, Landon C.
 8:00 AM-8:50 AM</t>
         </is>
       </c>
@@ -3264,7 +4288,7 @@
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>STAT 2163-002
 Bain, Leslie M.
@@ -3272,7 +4296,7 @@
         </is>
       </c>
       <c r="C5" s="6" t="n"/>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>STAT 2163-002
 Bain, Leslie M.
@@ -3280,7 +4304,7 @@
         </is>
       </c>
       <c r="E5" s="6" t="n"/>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>STAT 2163-002
 Bain, Leslie M.
@@ -3295,21 +4319,9 @@
         </is>
       </c>
       <c r="B6" s="6" t="n"/>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>MATH 1113-006
-Taylor, Teresa L.
-9:30 AM-10:50 AM</t>
-        </is>
-      </c>
+      <c r="C6" s="5" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>MATH 1113-006
-Taylor, Teresa L.
-9:30 AM-10:50 AM</t>
-        </is>
-      </c>
+      <c r="E6" s="5" t="n"/>
       <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -3318,26 +4330,26 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>MATH 1003-005
-Winn, Janet L.
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>MATH 1914-003
+Ballard, Kasey L.
 10:00 AM-10:50 AM</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>MATH 1003-005
-Winn, Janet L.
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>MATH 1914-003
+Ballard, Kasey L.
 10:00 AM-10:50 AM</t>
         </is>
       </c>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>MATH 1003-005
-Winn, Janet L.
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>MATH 1914-003
+Ballard, Kasey L.
 10:00 AM-10:50 AM</t>
         </is>
       </c>
@@ -3349,9 +4361,9 @@
         </is>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
+      <c r="C8" s="5" t="n"/>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
+      <c r="E8" s="5" t="n"/>
       <c r="F8" s="6" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -3360,38 +4372,38 @@
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>MATH 1113-001
-Yousuf, Marium
+Winn, Janet L.
 11:00 AM-11:50 AM</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>MATH 0903-001
-Yousuf, Marium
+Winn, Janet L.
 11:00 AM-12:20 PM</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>MATH 1113-001
-Yousuf, Marium
+Winn, Janet L.
 11:00 AM-11:50 AM</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>MATH 0903-001
-Yousuf, Marium
+Winn, Janet L.
 11:00 AM-12:20 PM</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>MATH 1113-001
-Yousuf, Marium
+Winn, Janet L.
 11:00 AM-11:50 AM</t>
         </is>
       </c>
@@ -3438,10 +4450,10 @@
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>MATH 2243-001
-Growns, Landon C.
+Overduin, Matthew D.
 1:00 PM-1:50 PM</t>
         </is>
       </c>
@@ -3452,10 +4464,10 @@
 1:00 PM-2:20 PM</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>MATH 2243-001
-Growns, Landon C.
+Overduin, Matthew D.
 1:00 PM-1:50 PM</t>
         </is>
       </c>
@@ -3466,10 +4478,10 @@
 1:00 PM-2:20 PM</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>MATH 2243-001
-Growns, Landon C.
+Overduin, Matthew D.
 1:00 PM-1:50 PM</t>
         </is>
       </c>
@@ -3560,7 +4572,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:F20"/>
-  <mergeCells count="24">
+  <mergeCells count="22">
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="F5:F6"/>
@@ -3571,13 +4583,11 @@
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="E3:E5"/>
     <mergeCell ref="D3:D4"/>
-    <mergeCell ref="C6:C8"/>
     <mergeCell ref="F13:F14"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="D9:D10"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="B5:B6"/>
-    <mergeCell ref="E6:E8"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="E13:E15"/>
     <mergeCell ref="A1:F1"/>
@@ -3611,7 +4621,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Room Schedule -- Corley 268</t>
+          <t>Room Schedule -- Corley 267</t>
         </is>
       </c>
     </row>
@@ -3653,32 +4663,11 @@
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>MATH 3203-001
-Overduin, Matthew D.
-8:00 AM-8:50 AM
-/ MATH 3203-H01</t>
-        </is>
-      </c>
+      <c r="B3" s="5" t="n"/>
       <c r="C3" s="5" t="n"/>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>MATH 3203-001
-Overduin, Matthew D.
-8:00 AM-8:50 AM
-/ MATH 3203-H01</t>
-        </is>
-      </c>
+      <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="n"/>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>MATH 3203-001
-Overduin, Matthew D.
-8:00 AM-8:50 AM
-/ MATH 3203-H01</t>
-        </is>
-      </c>
+      <c r="F3" s="5" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -3686,11 +4675,11 @@
           <t>8:30 AM</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="n"/>
+      <c r="D4" s="5" t="n"/>
       <c r="E4" s="5" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="F4" s="5" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -3722,26 +4711,26 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>MATH 1914-003
-Ballard, Kasey L.
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>MATH 1003-004
+Staff
 10:00 AM-10:50 AM</t>
         </is>
       </c>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>MATH 1914-003
-Ballard, Kasey L.
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>MATH 1003-004
+Staff
 10:00 AM-10:50 AM</t>
         </is>
       </c>
       <c r="E7" s="5" t="n"/>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>MATH 1914-003
-Ballard, Kasey L.
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>MATH 1003-004
+Staff
 10:00 AM-10:50 AM</t>
         </is>
       </c>
@@ -3764,11 +4753,29 @@
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n"/>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>MATH 0803-004
+Staff
+11:00 AM-11:50 AM</t>
+        </is>
+      </c>
       <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>MATH 0803-004
+Staff
+11:00 AM-11:50 AM</t>
+        </is>
+      </c>
       <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>MATH 0803-004
+Staff
+11:00 AM-11:50 AM</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -3776,11 +4783,11 @@
           <t>11:30 AM</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n"/>
+      <c r="B10" s="6" t="n"/>
       <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
+      <c r="D10" s="6" t="n"/>
       <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="F10" s="6" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -3905,12 +4912,12 @@
   </sheetData>
   <autoFilter ref="A2:F20"/>
   <mergeCells count="7">
-    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="F9:F10"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="B7:B8"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
     <mergeCell ref="F7:F8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3938,7 +4945,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Room Schedule -- Ross Pendergraft Library 220</t>
+          <t>Room Schedule -- Corley 268</t>
         </is>
       </c>
     </row>
@@ -4017,21 +5024,15 @@
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>MATH 2243-002
-Overduin, Matthew D.
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>MATH 1914-001
+Cox, Allie M.
 9:30 AM-10:50 AM</t>
         </is>
       </c>
       <c r="D6" s="5" t="n"/>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>MATH 2243-002
-Overduin, Matthew D.
-9:30 AM-10:50 AM</t>
-        </is>
-      </c>
+      <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -4040,29 +5041,11 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>MATH 1113-F01
-Yousuf, Marium
-10:00 AM-10:50 AM</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="n"/>
       <c r="C7" s="9" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>MATH 1113-F01
-Yousuf, Marium
-10:00 AM-10:50 AM</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>MATH 1113-F01
-Yousuf, Marium
-10:00 AM-10:50 AM</t>
-        </is>
-      </c>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -4070,11 +5053,11 @@
           <t>10:30 AM</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
+      <c r="B8" s="5" t="n"/>
       <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -4085,7 +5068,13 @@
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="5" t="n"/>
       <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>MATH 2934-002
+Limperis, Thomas G.
+11:00 AM-12:20 PM</t>
+        </is>
+      </c>
       <c r="F9" s="5" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -4097,7 +5086,7 @@
       <c r="B10" s="5" t="n"/>
       <c r="C10" s="5" t="n"/>
       <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
+      <c r="E10" s="9" t="n"/>
       <c r="F10" s="5" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -4109,7 +5098,7 @@
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="5" t="n"/>
       <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
+      <c r="E11" s="6" t="n"/>
       <c r="F11" s="5" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -4130,11 +5119,32 @@
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n"/>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>MATH 4123-001
+Limperis, Thomas G.
+1:00 PM-1:50 PM
+/ MATH 4123-H01</t>
+        </is>
+      </c>
       <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>MATH 4123-001
+Limperis, Thomas G.
+1:00 PM-1:50 PM
+/ MATH 4123-H01</t>
+        </is>
+      </c>
       <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>MATH 4123-001
+Limperis, Thomas G.
+1:00 PM-1:50 PM
+/ MATH 4123-H01</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -4142,11 +5152,11 @@
           <t>1:30 PM</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n"/>
+      <c r="B14" s="6" t="n"/>
       <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
+      <c r="D14" s="6" t="n"/>
       <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
+      <c r="F14" s="6" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -4223,12 +5233,12 @@
   </sheetData>
   <autoFilter ref="A2:F20"/>
   <mergeCells count="6">
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="B13:B14"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="D13:D14"/>
     <mergeCell ref="C6:C8"/>
-    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="E9:E11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -4255,7 +5265,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Room Schedule -- Ross Pendergraft Library 331</t>
+          <t>Room Schedule -- Corley 269</t>
         </is>
       </c>
     </row>
@@ -4297,29 +5307,11 @@
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>MATH 1003-002
-Growns, Landon C.
-8:00 AM-8:50 AM</t>
-        </is>
-      </c>
+      <c r="B3" s="5" t="n"/>
       <c r="C3" s="5" t="n"/>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>MATH 1003-002
-Growns, Landon C.
-8:00 AM-8:50 AM</t>
-        </is>
-      </c>
+      <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="n"/>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>MATH 1003-002
-Growns, Landon C.
-8:00 AM-8:50 AM</t>
-        </is>
-      </c>
+      <c r="F3" s="5" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -4327,11 +5319,11 @@
           <t>8:30 AM</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="n"/>
+      <c r="D4" s="5" t="n"/>
       <c r="E4" s="5" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="F4" s="5" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -4339,29 +5331,11 @@
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>MATH 0803-002
-Growns, Landon C.
-9:00 AM-9:50 AM</t>
-        </is>
-      </c>
+      <c r="B5" s="5" t="n"/>
       <c r="C5" s="5" t="n"/>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>MATH 0803-002
-Growns, Landon C.
-9:00 AM-9:50 AM</t>
-        </is>
-      </c>
+      <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>MATH 0803-002
-Growns, Landon C.
-9:00 AM-9:50 AM</t>
-        </is>
-      </c>
+      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -4369,11 +5343,11 @@
           <t>9:30 AM</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n"/>
+      <c r="B6" s="5" t="n"/>
       <c r="C6" s="5" t="n"/>
-      <c r="D6" s="6" t="n"/>
+      <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
-      <c r="F6" s="6" t="n"/>
+      <c r="F6" s="5" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -4381,11 +5355,29 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n"/>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>MATH 1113-F01
+Yousuf, Marium
+10:00 AM-10:50 AM</t>
+        </is>
+      </c>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>MATH 1113-F01
+Yousuf, Marium
+10:00 AM-10:50 AM</t>
+        </is>
+      </c>
       <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>MATH 1113-F01
+Yousuf, Marium
+10:00 AM-10:50 AM</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -4393,11 +5385,11 @@
           <t>10:30 AM</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n"/>
+      <c r="B8" s="6" t="n"/>
       <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
+      <c r="D8" s="6" t="n"/>
       <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="F8" s="6" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -4405,11 +5397,29 @@
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n"/>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>STAT 3153-002
+Jordan, Scott M.
+11:00 AM-11:50 AM</t>
+        </is>
+      </c>
       <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>STAT 3153-002
+Jordan, Scott M.
+11:00 AM-11:50 AM</t>
+        </is>
+      </c>
       <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>STAT 3153-002
+Jordan, Scott M.
+11:00 AM-11:50 AM</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -4417,11 +5427,11 @@
           <t>11:30 AM</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n"/>
+      <c r="B10" s="6" t="n"/>
       <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
+      <c r="D10" s="6" t="n"/>
       <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="F10" s="6" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -4546,13 +5556,13 @@
   </sheetData>
   <autoFilter ref="A2:F20"/>
   <mergeCells count="7">
-    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="F9:F10"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="F7:F8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -4579,7 +5589,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Room Schedule -- Rothwell 206</t>
+          <t>Room Schedule -- Ross Pendergraft Library 220</t>
         </is>
       </c>
     </row>
@@ -4621,29 +5631,11 @@
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>MATH 2924-002
-Yousuf, Marium
-8:00 AM-8:50 AM</t>
-        </is>
-      </c>
+      <c r="B3" s="5" t="n"/>
       <c r="C3" s="5" t="n"/>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>MATH 2924-002
-Yousuf, Marium
-8:00 AM-8:50 AM</t>
-        </is>
-      </c>
+      <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="n"/>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>MATH 2924-002
-Yousuf, Marium
-8:00 AM-8:50 AM</t>
-        </is>
-      </c>
+      <c r="F3" s="5" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -4651,11 +5643,11 @@
           <t>8:30 AM</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="n"/>
+      <c r="D4" s="5" t="n"/>
       <c r="E4" s="5" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="F4" s="5" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -4663,29 +5655,11 @@
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>MATH 4003-001
-Xiao, Xinli
-9:00 AM-9:50 AM</t>
-        </is>
-      </c>
+      <c r="B5" s="5" t="n"/>
       <c r="C5" s="5" t="n"/>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>MATH 4003-001
-Xiao, Xinli
-9:00 AM-9:50 AM</t>
-        </is>
-      </c>
+      <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>MATH 4003-001
-Xiao, Xinli
-9:00 AM-9:50 AM</t>
-        </is>
-      </c>
+      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -4693,17 +5667,23 @@
           <t>9:30 AM</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>MATH 2924-003
-Limperis, Thomas G.
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>MATH 2243-002
+Overduin, Matthew D.
 9:30 AM-10:50 AM</t>
         </is>
       </c>
-      <c r="F6" s="6" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>MATH 2243-002
+Overduin, Matthew D.
+9:30 AM-10:50 AM</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -4711,29 +5691,11 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>MATH 3243-001
-Xiao, Xinli
-10:00 AM-10:50 AM</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>MATH 3243-001
-Xiao, Xinli
-10:00 AM-10:50 AM</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="5" t="n"/>
       <c r="E7" s="9" t="n"/>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>MATH 3243-001
-Xiao, Xinli
-10:00 AM-10:50 AM</t>
-        </is>
-      </c>
+      <c r="F7" s="5" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -4741,11 +5703,11 @@
           <t>10:30 AM</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="6" t="n"/>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="5" t="n"/>
       <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
+      <c r="F8" s="5" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -4754,21 +5716,9 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>MATH 2703-002
-Limperis, Thomas G.
-11:00 AM-12:20 PM</t>
-        </is>
-      </c>
+      <c r="C9" s="5" t="n"/>
       <c r="D9" s="5" t="n"/>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>MATH 2703-002
-Limperis, Thomas G.
-11:00 AM-12:20 PM</t>
-        </is>
-      </c>
+      <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -4778,9 +5728,9 @@
         </is>
       </c>
       <c r="B10" s="5" t="n"/>
-      <c r="C10" s="9" t="n"/>
+      <c r="C10" s="5" t="n"/>
       <c r="D10" s="5" t="n"/>
-      <c r="E10" s="9" t="n"/>
+      <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -4790,9 +5740,9 @@
         </is>
       </c>
       <c r="B11" s="5" t="n"/>
-      <c r="C11" s="6" t="n"/>
+      <c r="C11" s="5" t="n"/>
       <c r="D11" s="5" t="n"/>
-      <c r="E11" s="6" t="n"/>
+      <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -4814,13 +5764,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n"/>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>MATH 2924-002
-Yousuf, Marium
-1:00 PM-2:20 PM</t>
-        </is>
-      </c>
+      <c r="C13" s="5" t="n"/>
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
@@ -4832,7 +5776,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n"/>
-      <c r="C14" s="9" t="n"/>
+      <c r="C14" s="5" t="n"/>
       <c r="D14" s="5" t="n"/>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
@@ -4844,7 +5788,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n"/>
-      <c r="C15" s="6" t="n"/>
+      <c r="C15" s="5" t="n"/>
       <c r="D15" s="5" t="n"/>
       <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n"/>
@@ -4911,21 +5855,10 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:F20"/>
-  <mergeCells count="14">
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="E9:E11"/>
-    <mergeCell ref="B3:B4"/>
+  <mergeCells count="3">
+    <mergeCell ref="C6:C8"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="F5:F6"/>
     <mergeCell ref="E6:E8"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -4952,7 +5885,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Room Schedule -- Rothwell 207</t>
+          <t>Room Schedule -- Ross Pendergraft Library 331</t>
         </is>
       </c>
     </row>
@@ -5018,26 +5951,26 @@
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>STAT 3153-001
-Jordan, Scott M.
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>MATH 0803-002
+Growns, Landon C.
 9:00 AM-9:50 AM</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>STAT 3153-001
-Jordan, Scott M.
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>MATH 0803-002
+Growns, Landon C.
 9:00 AM-9:50 AM</t>
         </is>
       </c>
       <c r="E5" s="5" t="n"/>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>STAT 3153-001
-Jordan, Scott M.
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>MATH 0803-002
+Growns, Landon C.
 9:00 AM-9:50 AM</t>
         </is>
       </c>
@@ -5049,13 +5982,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n"/>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>MATH 2934-001
-Staff
-9:30 AM-10:50 AM</t>
-        </is>
-      </c>
+      <c r="C6" s="5" t="n"/>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="6" t="n"/>
@@ -5066,26 +5993,26 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>MATH 2934-001
-Staff
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>MATH 1003-002
+Growns, Landon C.
 10:00 AM-10:50 AM</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>MATH 2934-001
-Staff
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>MATH 1003-002
+Growns, Landon C.
 10:00 AM-10:50 AM</t>
         </is>
       </c>
       <c r="E7" s="5" t="n"/>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>MATH 2934-001
-Staff
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>MATH 1003-002
+Growns, Landon C.
 10:00 AM-10:50 AM</t>
         </is>
       </c>
@@ -5097,7 +6024,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
+      <c r="C8" s="5" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="6" t="n"/>
@@ -5248,13 +6175,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:F20"/>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="C6:C8"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
   </mergeCells>
